--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>82.22776021328987</v>
+        <v>13.3620110346596</v>
       </c>
       <c r="D2" t="n">
-        <v>82.05698202949817</v>
+        <v>13.33425957979345</v>
       </c>
       <c r="E2" t="n">
-        <v>5.721765195867778</v>
+        <v>0.9297868443285136</v>
       </c>
       <c r="F2" t="n">
-        <v>5.48108153081423</v>
+        <v>0.8906757487573126</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>73.50884032561689</v>
+        <v>11.94518655291274</v>
       </c>
       <c r="D3" t="n">
-        <v>73.57192145643984</v>
+        <v>11.95543723667147</v>
       </c>
       <c r="E3" t="n">
-        <v>5.721765195867778</v>
+        <v>0.9297868443285136</v>
       </c>
       <c r="F3" t="n">
-        <v>5.48108153081423</v>
+        <v>0.8906757487573126</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>76.05592499188879</v>
+        <v>12.35908781118193</v>
       </c>
       <c r="D4" t="n">
-        <v>76.19088603664103</v>
+        <v>12.38101898095417</v>
       </c>
       <c r="E4" t="n">
-        <v>5.721765195867778</v>
+        <v>0.9297868443285136</v>
       </c>
       <c r="F4" t="n">
-        <v>5.48108153081423</v>
+        <v>0.8906757487573126</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>66.26388408634334</v>
+        <v>10.76788116403079</v>
       </c>
       <c r="D5" t="n">
-        <v>66.79066921254058</v>
+        <v>10.85348374703784</v>
       </c>
       <c r="E5" t="n">
-        <v>5.721765195867778</v>
+        <v>0.9297868443285136</v>
       </c>
       <c r="F5" t="n">
-        <v>5.48108153081423</v>
+        <v>0.8906757487573126</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
